--- a/output_data/charts/1600000US3963030.xlsx
+++ b/output_data/charts/1600000US3963030.xlsx
@@ -14,12 +14,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
   <si>
     <t>Historical</t>
-  </si>
-  <si>
-    <t>Forecast</t>
   </si>
   <si>
     <t>Date</t>
@@ -169,10 +166,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$12</c:f>
+              <c:f>Sheet1!$A$2:$A$6</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>36708</c:v>
                 </c:pt>
@@ -187,34 +184,16 @@
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>44013</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>45839</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>47665</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>49491</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>51318</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>53144</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>54970</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$2:$B$12</c:f>
+              <c:f>Sheet1!$B$2:$B$6</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>2882</c:v>
                 </c:pt>
@@ -228,110 +207,7 @@
                   <c:v>3994</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>4144</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$C$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Forecast</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="38100">
-              <a:solidFill>
-                <a:srgbClr val="2C7F68"/>
-              </a:solidFill>
-            </a:ln>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="7"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="2C7F68"/>
-              </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-            </c:spPr>
-          </c:marker>
-          <c:cat>
-            <c:numRef>
-              <c:f>Sheet1!$A$2:$A$12</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
-                <c:pt idx="0">
-                  <c:v>36708</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>38534</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>40360</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>42186</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>44013</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>45839</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>47665</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>49491</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>51318</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>53144</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>54970</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Sheet1!$C$2:$C$12</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
-                <c:pt idx="5">
-                  <c:v>4370</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>4762</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>5226</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>5604</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>5917</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>6195</c:v>
+                  <c:v>4151</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -374,7 +250,7 @@
         <c:axId val="50010002"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="6814.500000000001"/>
+          <c:max val="4798.200000000001"/>
           <c:min val="0"/>
         </c:scaling>
         <c:axPos val="l"/>
@@ -428,13 +304,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
+      <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
+      <xdr:col>14</xdr:col>
       <xdr:colOff>152400</xdr:colOff>
       <xdr:row>21</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
@@ -744,26 +620,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="1" customWidth="1"/>
     <col min="2" max="2" width="20.7109375" style="2" customWidth="1"/>
-    <col min="3" max="3" width="20.7109375" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:2">
       <c r="A1" s="3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>1</v>
-      </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:2">
       <c r="A2" s="4">
         <v>36708</v>
       </c>
@@ -771,7 +643,7 @@
         <v>2882</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:2">
       <c r="A3" s="4">
         <v>38534</v>
       </c>
@@ -779,7 +651,7 @@
         <v>3563</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:2">
       <c r="A4" s="4">
         <v>40360</v>
       </c>
@@ -787,7 +659,7 @@
         <v>4196</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:2">
       <c r="A5" s="4">
         <v>42186</v>
       </c>
@@ -795,60 +667,12 @@
         <v>3994</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:2">
       <c r="A6" s="4">
         <v>44013</v>
       </c>
       <c r="B6" s="2">
-        <v>4144</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="4">
-        <v>45839</v>
-      </c>
-      <c r="C7" s="2">
-        <v>4370</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="4">
-        <v>47665</v>
-      </c>
-      <c r="C8" s="2">
-        <v>4762</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="4">
-        <v>49491</v>
-      </c>
-      <c r="C9" s="2">
-        <v>5226</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="4">
-        <v>51318</v>
-      </c>
-      <c r="C10" s="2">
-        <v>5604</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="4">
-        <v>53144</v>
-      </c>
-      <c r="C11" s="2">
-        <v>5917</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="4">
-        <v>54970</v>
-      </c>
-      <c r="C12" s="2">
-        <v>6195</v>
+        <v>4151</v>
       </c>
     </row>
   </sheetData>
